--- a/ttl_long/AdHoc_Net_14.xlsx
+++ b/ttl_long/AdHoc_Net_14.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>78</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>224</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>79</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>138</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>197</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>221</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>317</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>142</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>351</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>265</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>426</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>324</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>454</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>264</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>511</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>330</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>463</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>623</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>201</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>576</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>349</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>642</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>967</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>267</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>830</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>310</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>815</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>1013</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>113</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>1137</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>335</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>1030</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1271</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1165</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>311</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1224</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1383</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>215</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1355</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1389</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>414</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -936,80 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1372</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1499</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1487</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>391</t>
+          <t>1271</t>
         </is>
       </c>
     </row>
@@ -1024,7 +956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,7 +989,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1101,7 +1033,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1123,7 +1055,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1167,7 +1099,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,7 +1121,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1211,7 +1143,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1233,7 +1165,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1255,7 +1187,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1277,7 +1209,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1299,7 +1231,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1343,7 +1275,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1365,7 +1297,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1387,7 +1319,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1409,7 +1341,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1431,7 +1363,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1448,12 +1380,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1475,7 +1407,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1497,7 +1429,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1519,7 +1451,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1541,7 +1473,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1563,7 +1495,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1580,12 +1512,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1602,12 +1534,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1629,7 +1561,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1646,12 +1578,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1668,12 +1600,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1690,12 +1622,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1712,12 +1644,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1734,12 +1666,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1756,12 +1688,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1778,12 +1710,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1800,12 +1732,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1822,12 +1754,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1844,12 +1776,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1871,7 +1803,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1893,7 +1825,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1910,12 +1842,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1932,12 +1864,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1954,12 +1886,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1981,7 +1913,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2003,7 +1935,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2020,12 +1952,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2047,7 +1979,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2069,7 +2001,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2086,12 +2018,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2108,12 +2040,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2135,7 +2067,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2152,12 +2084,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2174,12 +2106,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2196,12 +2128,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2218,12 +2150,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2245,7 +2177,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2267,7 +2199,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2289,7 +2221,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2311,7 +2243,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2333,7 +2265,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2350,7 +2282,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2394,12 +2326,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2416,12 +2348,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2443,7 +2375,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2487,7 +2419,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2509,7 +2441,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2531,7 +2463,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2548,12 +2480,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2575,7 +2507,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2592,12 +2524,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2619,7 +2551,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2636,12 +2568,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2658,12 +2590,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2680,12 +2612,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2702,12 +2634,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2724,12 +2656,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2746,12 +2678,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2768,12 +2700,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2782,292 +2714,6 @@
         </is>
       </c>
       <c r="D80" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3116,7 +2762,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -3142,7 +2788,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_14.xlsx
+++ b/ttl_long/AdHoc_Net_14.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>66</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>196</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>103</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>198</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>306</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>152</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>91</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>193</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>264</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>264</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>448</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>193</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>332</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>339</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>410</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>116</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>584</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>269</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>519</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>454</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>105</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>664</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>130</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>549</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>647</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>787</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>266</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>735</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>305</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>737</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>883</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>135</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>835</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>828</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>945</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>245</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1053</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1016</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>1154</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>206</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>1181</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,199 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>328</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1128</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1371</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1489</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1524</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1639</t>
         </is>
       </c>
     </row>
@@ -956,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1099,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1121,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1165,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1187,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1231,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1248,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1275,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1319,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1341,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1363,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1380,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1407,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1424,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1446,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1473,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1495,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1512,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1534,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1556,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1578,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1600,12 +1787,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1622,12 +1809,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1644,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1666,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1688,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1710,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1732,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1754,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1776,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1803,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1820,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1842,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1864,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1886,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1913,7 +2100,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1930,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1952,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1979,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2001,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2018,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2040,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2062,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2084,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2106,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2128,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2150,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2177,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2199,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2221,7 +2408,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2243,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2260,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2282,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2309,7 +2496,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2353,7 +2540,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2375,7 +2562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2397,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2419,7 +2606,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2441,7 +2628,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2463,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2485,7 +2672,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2529,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2551,7 +2738,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2568,7 +2755,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2595,7 +2782,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2612,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2634,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2656,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2678,12 +2865,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2700,20 +2887,812 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2762,7 +3741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -2782,7 +3761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_14.xlsx
+++ b/ttl_long/AdHoc_Net_14.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>160</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>1637</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>84</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>136</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>190</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>286</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>325</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>122</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>252</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>285</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>327</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>354</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>348</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>82</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>557</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>127</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>501</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>298</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>483</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>590</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>246</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>591</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>653</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>698</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>112</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>809</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>351</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>709</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>874</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>899</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>327</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>897</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>1029</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>151</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>986</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>391</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1007</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1098</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1181</t>
+          <t>1044</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1154</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1175</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>170</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1194</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1283</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1347</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>69</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1358</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1337</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1411</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>189</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1515</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>347</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1502</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1587</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>128</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1650</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D116"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1611,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1633,12 +1633,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1655,12 +1655,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1743,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1765,12 +1765,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1875,12 +1875,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1897,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2183,7 +2183,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2249,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2381,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2403,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2425,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2557,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2623,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2667,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2843,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,12 +2909,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,12 +2975,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2997,12 +2997,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3063,12 +3063,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3151,12 +3151,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3239,12 +3239,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3349,12 +3349,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3459,12 +3459,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3481,12 +3481,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3503,12 +3503,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3547,12 +3547,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3569,12 +3569,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3583,116 +3583,6 @@
         </is>
       </c>
       <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3731,7 +3621,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3741,7 +3631,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
